--- a/jogos_2025-04-17.xlsx
+++ b/jogos_2025-04-17.xlsx
@@ -901,109 +901,109 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Lyngby</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="M4" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="N4" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="O4" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="P4" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S4" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="X4" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AA4" t="n">
         <v>3</v>
       </c>
-      <c r="H4" t="n">
-        <v>3</v>
-      </c>
-      <c r="I4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J4" t="n">
-        <v>2</v>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L4" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="M4" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="N4" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="O4" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="P4" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S4" t="n">
-        <v>3.56</v>
-      </c>
-      <c r="T4" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X4" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="Z4" t="n">
+      <c r="AB4" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>['15', '84']</t>
+        </is>
+      </c>
+      <c r="AG4" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AJ4" t="n">
         <v>2.2</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>['21', '55', '60']</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>['27', '39', '85']</t>
-        </is>
-      </c>
-      <c r="AG4" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>1.83</v>
       </c>
       <c r="AK4" s="3" t="n">
         <v>45764.375</v>
@@ -1159,109 +1159,109 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Lyngby</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H6" t="n">
+        <v>3</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" t="n">
         <v>2</v>
       </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>1</v>
-      </c>
       <c r="K6" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.15</v>
+        <v>3.15</v>
       </c>
       <c r="M6" t="n">
-        <v>3.32</v>
+        <v>3.94</v>
       </c>
       <c r="N6" t="n">
-        <v>3.15</v>
+        <v>2.12</v>
       </c>
       <c r="O6" t="n">
-        <v>2.7</v>
+        <v>3.6</v>
       </c>
       <c r="P6" t="n">
-        <v>2.12</v>
+        <v>2.28</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.55</v>
+        <v>2.65</v>
       </c>
       <c r="R6" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="S6" t="n">
-        <v>2.9</v>
+        <v>3.56</v>
       </c>
       <c r="T6" t="n">
-        <v>2.78</v>
+        <v>2.34</v>
       </c>
       <c r="U6" t="n">
-        <v>1.39</v>
+        <v>1.5</v>
       </c>
       <c r="V6" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W6" t="n">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="X6" t="n">
-        <v>3.98</v>
+        <v>4.33</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.8</v>
+        <v>1.62</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="AA6" t="n">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="AD6" t="n">
-        <v>2.1</v>
+        <v>2.43</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['21', '55', '60']</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>['15', '84']</t>
+          <t>['27', '39', '85']</t>
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.69</v>
+        <v>1.33</v>
       </c>
       <c r="AI6" t="n">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="AJ6" t="n">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="AK6" s="3" t="n">
         <v>45764.375</v>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Nassaji Mazandaran</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,65 +1443,65 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="M8" t="n">
-        <v>2.6</v>
+        <v>2.41</v>
       </c>
       <c r="N8" t="n">
-        <v>3.3</v>
+        <v>4.4</v>
       </c>
       <c r="O8" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="P8" t="n">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.33</v>
+        <v>5.25</v>
       </c>
       <c r="R8" t="n">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="S8" t="n">
-        <v>2.01</v>
+        <v>1.87</v>
       </c>
       <c r="T8" t="n">
-        <v>4.33</v>
+        <v>4.9</v>
       </c>
       <c r="U8" t="n">
         <v>1.15</v>
       </c>
       <c r="V8" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="W8" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="X8" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="Y8" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AA8" t="n">
-        <v>6.75</v>
+        <v>7.1</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="AC8" t="n">
         <v>2.45</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>['37']</t>
+          <t>['45+7']</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -1510,16 +1510,16 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.3</v>
+        <v>1.58</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.47</v>
+        <v>1.58</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="AK8" s="3" t="n">
         <v>45764.4375</v>
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Nassaji Mazandaran</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,65 +1572,65 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="M9" t="n">
-        <v>2.41</v>
+        <v>2.6</v>
       </c>
       <c r="N9" t="n">
-        <v>4.4</v>
+        <v>3.3</v>
       </c>
       <c r="O9" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="P9" t="n">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="Q9" t="n">
-        <v>5.25</v>
+        <v>4.33</v>
       </c>
       <c r="R9" t="n">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="S9" t="n">
-        <v>1.87</v>
+        <v>2.01</v>
       </c>
       <c r="T9" t="n">
-        <v>4.9</v>
+        <v>4.33</v>
       </c>
       <c r="U9" t="n">
         <v>1.15</v>
       </c>
       <c r="V9" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="W9" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="X9" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="Y9" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AA9" t="n">
-        <v>7.1</v>
+        <v>6.75</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="AC9" t="n">
         <v>2.45</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>['45+7']</t>
+          <t>['37']</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -1639,16 +1639,16 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.58</v>
+        <v>1.3</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.58</v>
+        <v>1.47</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AJ9" t="n">
-        <v>3.2</v>
+        <v>2.88</v>
       </c>
       <c r="AK9" s="3" t="n">
         <v>45764.4375</v>
@@ -2062,109 +2062,109 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
         <v>1</v>
       </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
       <c r="K13" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.8</v>
+        <v>1.33</v>
       </c>
       <c r="M13" t="n">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="N13" t="n">
-        <v>3.5</v>
+        <v>6.5</v>
       </c>
       <c r="O13" t="n">
-        <v>2.1</v>
+        <v>1.79</v>
       </c>
       <c r="P13" t="n">
-        <v>2.38</v>
+        <v>2.62</v>
       </c>
       <c r="Q13" t="n">
-        <v>5</v>
+        <v>6.1</v>
       </c>
       <c r="R13" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="S13" t="n">
-        <v>3.04</v>
+        <v>3.6</v>
       </c>
       <c r="T13" t="n">
-        <v>2.45</v>
+        <v>2.15</v>
       </c>
       <c r="U13" t="n">
-        <v>1.48</v>
+        <v>1.62</v>
       </c>
       <c r="V13" t="n">
         <v>1.01</v>
       </c>
       <c r="W13" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="X13" t="n">
-        <v>3.8</v>
+        <v>4.75</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.7</v>
+        <v>1.53</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.95</v>
+        <v>2.37</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.65</v>
+        <v>2.2</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.42</v>
+        <v>1.59</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.93</v>
+        <v>2.06</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>['14', '57', '68', '77']</t>
+          <t>['65']</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['13']</t>
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.22</v>
+        <v>1.06</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.2</v>
+        <v>3.25</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.57</v>
+        <v>1.33</v>
       </c>
       <c r="AJ13" t="n">
-        <v>2.4</v>
+        <v>3.25</v>
       </c>
       <c r="AK13" s="3" t="n">
         <v>45764.45833333334</v>
@@ -2310,35 +2310,35 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Aqaba</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="G15" t="n">
+        <v>4</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
         <v>1</v>
       </c>
-      <c r="H15" t="n">
-        <v>3</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
       <c r="J15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -2346,83 +2346,83 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="M15" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="N15" t="n">
-        <v>5.46</v>
+        <v>3.5</v>
       </c>
       <c r="O15" t="n">
-        <v>1.83</v>
+        <v>2.1</v>
       </c>
       <c r="P15" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="Q15" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R15" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="S15" t="n">
-        <v>2.76</v>
+        <v>3.04</v>
       </c>
       <c r="T15" t="n">
-        <v>2.69</v>
+        <v>2.45</v>
       </c>
       <c r="U15" t="n">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="V15" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W15" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="X15" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="AA15" t="n">
-        <v>3.2</v>
+        <v>2.65</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.84</v>
+        <v>1.74</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.75</v>
+        <v>1.93</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>['88']</t>
+          <t>['14', '57', '68', '77']</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>['26', '36', '81']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.11</v>
+        <v>1.22</v>
       </c>
       <c r="AH15" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AJ15" t="n">
         <v>2.4</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>3</v>
       </c>
       <c r="AK15" s="3" t="n">
         <v>45764.45833333334</v>
@@ -2439,35 +2439,35 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>Aqaba</t>
         </is>
       </c>
       <c r="G16" t="n">
         <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -2475,83 +2475,83 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="M16" t="n">
-        <v>4.8</v>
+        <v>3.9</v>
       </c>
       <c r="N16" t="n">
-        <v>6.5</v>
+        <v>5.46</v>
       </c>
       <c r="O16" t="n">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="P16" t="n">
-        <v>2.62</v>
+        <v>2.25</v>
       </c>
       <c r="Q16" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="R16" t="n">
-        <v>1.22</v>
+        <v>1.37</v>
       </c>
       <c r="S16" t="n">
-        <v>3.6</v>
+        <v>2.76</v>
       </c>
       <c r="T16" t="n">
-        <v>2.15</v>
+        <v>2.69</v>
       </c>
       <c r="U16" t="n">
-        <v>1.62</v>
+        <v>1.38</v>
       </c>
       <c r="V16" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W16" t="n">
-        <v>1.15</v>
+        <v>1.24</v>
       </c>
       <c r="X16" t="n">
-        <v>4.75</v>
+        <v>3.75</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.53</v>
+        <v>1.85</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.37</v>
+        <v>1.88</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.2</v>
+        <v>3.2</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.59</v>
+        <v>1.3</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.71</v>
+        <v>1.84</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.06</v>
+        <v>1.75</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>['65']</t>
+          <t>['88']</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>['13']</t>
+          <t>['26', '36', '81']</t>
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AH16" t="n">
-        <v>3.25</v>
+        <v>2.4</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AJ16" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45764.45833333334</v>
@@ -3352,22 +3352,22 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -3378,83 +3378,83 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.14</v>
+        <v>1.6</v>
       </c>
       <c r="M23" t="n">
-        <v>7.9</v>
+        <v>4.16</v>
       </c>
       <c r="N23" t="n">
-        <v>12.9</v>
+        <v>4.8</v>
       </c>
       <c r="O23" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="P23" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S23" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="X23" t="n">
+        <v>4.16</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AB23" t="n">
         <v>1.45</v>
       </c>
-      <c r="P23" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>9</v>
-      </c>
-      <c r="R23" t="n">
+      <c r="AC23" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG23" t="n">
         <v>1.17</v>
       </c>
-      <c r="S23" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="T23" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X23" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>3.39</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AE23" t="inlineStr">
-        <is>
-          <t>['26', '84', '88']</t>
-        </is>
-      </c>
-      <c r="AF23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG23" t="n">
-        <v>1.03</v>
-      </c>
       <c r="AH23" t="n">
-        <v>5</v>
+        <v>2.2</v>
       </c>
       <c r="AI23" t="n">
-        <v>1.22</v>
+        <v>1.53</v>
       </c>
       <c r="AJ23" t="n">
-        <v>4.2</v>
+        <v>2.8</v>
       </c>
       <c r="AK23" s="3" t="n">
         <v>45764.53472222222</v>
@@ -3481,22 +3481,22 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -3507,83 +3507,83 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.6</v>
+        <v>1.14</v>
       </c>
       <c r="M24" t="n">
-        <v>4.16</v>
+        <v>7.9</v>
       </c>
       <c r="N24" t="n">
-        <v>4.8</v>
+        <v>12.9</v>
       </c>
       <c r="O24" t="n">
-        <v>2.1</v>
+        <v>1.45</v>
       </c>
       <c r="P24" t="n">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
       <c r="Q24" t="n">
-        <v>4.75</v>
+        <v>9</v>
       </c>
       <c r="R24" t="n">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="S24" t="n">
-        <v>3.2</v>
+        <v>4.5</v>
       </c>
       <c r="T24" t="n">
-        <v>2.38</v>
+        <v>1.8</v>
       </c>
       <c r="U24" t="n">
-        <v>1.53</v>
+        <v>1.91</v>
       </c>
       <c r="V24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X24" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>['26', '84', '88']</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG24" t="n">
         <v>1.03</v>
       </c>
-      <c r="W24" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="X24" t="n">
-        <v>4.16</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AE24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG24" t="n">
-        <v>1.17</v>
-      </c>
       <c r="AH24" t="n">
-        <v>2.2</v>
+        <v>5</v>
       </c>
       <c r="AI24" t="n">
-        <v>1.53</v>
+        <v>1.22</v>
       </c>
       <c r="AJ24" t="n">
-        <v>2.8</v>
+        <v>4.2</v>
       </c>
       <c r="AK24" s="3" t="n">
         <v>45764.53472222222</v>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,109 +3610,109 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Suduroy</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L25" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="M25" t="n">
+        <v>12</v>
+      </c>
+      <c r="N25" t="n">
+        <v>26</v>
+      </c>
+      <c r="O25" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="P25" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>9</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="U25" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X25" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>['79']</t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG25" t="n">
         <v>1</v>
       </c>
-      <c r="I25" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L25" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="M25" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="N25" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="O25" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="P25" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="R25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S25" t="n">
-        <v>0</v>
-      </c>
-      <c r="T25" t="n">
-        <v>0</v>
-      </c>
-      <c r="U25" t="n">
-        <v>0</v>
-      </c>
-      <c r="V25" t="n">
-        <v>0</v>
-      </c>
-      <c r="W25" t="n">
-        <v>0</v>
-      </c>
-      <c r="X25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE25" t="inlineStr">
-        <is>
-          <t>['52', '56']</t>
-        </is>
-      </c>
-      <c r="AF25" t="inlineStr">
-        <is>
-          <t>['90+4']</t>
-        </is>
-      </c>
-      <c r="AG25" t="n">
-        <v>0</v>
-      </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AI25" t="n">
-        <v>2.38</v>
+        <v>1.18</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1.83</v>
+        <v>4.5</v>
       </c>
       <c r="AK25" s="3" t="n">
         <v>45764.54166666666</v>
@@ -3729,119 +3729,119 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Šibenik</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Suduroy</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="n">
+        <v>4</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
         <v>1</v>
       </c>
-      <c r="H26" t="n">
-        <v>0</v>
-      </c>
-      <c r="I26" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0</v>
-      </c>
       <c r="K26" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.04</v>
+        <v>8</v>
       </c>
       <c r="M26" t="n">
-        <v>12</v>
+        <v>4.1</v>
       </c>
       <c r="N26" t="n">
-        <v>26</v>
+        <v>1.43</v>
       </c>
       <c r="O26" t="n">
-        <v>1.25</v>
+        <v>6</v>
       </c>
       <c r="P26" t="n">
-        <v>4.2</v>
+        <v>2.25</v>
       </c>
       <c r="Q26" t="n">
-        <v>9</v>
+        <v>1.96</v>
       </c>
       <c r="R26" t="n">
-        <v>1.12</v>
+        <v>1.33</v>
       </c>
       <c r="S26" t="n">
-        <v>5.05</v>
+        <v>3</v>
       </c>
       <c r="T26" t="n">
-        <v>1.54</v>
+        <v>2.73</v>
       </c>
       <c r="U26" t="n">
-        <v>2.25</v>
+        <v>1.4</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W26" t="n">
-        <v>1.02</v>
+        <v>1.28</v>
       </c>
       <c r="X26" t="n">
-        <v>15</v>
+        <v>3.44</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.14</v>
+        <v>1.85</v>
       </c>
       <c r="Z26" t="n">
-        <v>5</v>
+        <v>1.9</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.37</v>
+        <v>2.8</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.7</v>
+        <v>1.33</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="AD26" t="n">
         <v>1.67</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>['79']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['14', '48', '70', '84']</t>
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AH26" t="n">
-        <v>11</v>
+        <v>1.08</v>
       </c>
       <c r="AI26" t="n">
-        <v>1.18</v>
+        <v>3.95</v>
       </c>
       <c r="AJ26" t="n">
-        <v>4.5</v>
+        <v>1.3</v>
       </c>
       <c r="AK26" s="3" t="n">
         <v>45764.54166666666</v>
@@ -3858,119 +3858,119 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H27" t="n">
+        <v>1</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L27" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="M27" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N27" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="O27" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="P27" t="n">
         <v>2</v>
       </c>
-      <c r="I27" t="n">
-        <v>2</v>
-      </c>
-      <c r="J27" t="n">
-        <v>0</v>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L27" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="M27" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="N27" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="O27" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="P27" t="n">
-        <v>2.04</v>
-      </c>
       <c r="Q27" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="R27" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>['52', '56']</t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>['90+4']</t>
+        </is>
+      </c>
+      <c r="AG27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AJ27" t="n">
         <v>1.83</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AE27" t="inlineStr">
-        <is>
-          <t>['29', '39', '86', '90+1']</t>
-        </is>
-      </c>
-      <c r="AF27" t="inlineStr">
-        <is>
-          <t>['56', '78']</t>
-        </is>
-      </c>
-      <c r="AG27" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>1.98</v>
       </c>
       <c r="AK27" s="3" t="n">
         <v>45764.54166666666</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,25 +3997,25 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Šibenik</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H28" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -4023,83 +4023,83 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>8</v>
+        <v>2.4</v>
       </c>
       <c r="M28" t="n">
-        <v>4.1</v>
+        <v>3.25</v>
       </c>
       <c r="N28" t="n">
-        <v>1.43</v>
+        <v>2.83</v>
       </c>
       <c r="O28" t="n">
-        <v>6</v>
+        <v>2.9</v>
       </c>
       <c r="P28" t="n">
-        <v>2.25</v>
+        <v>2.04</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.96</v>
+        <v>3.3</v>
       </c>
       <c r="R28" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="S28" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="T28" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="U28" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="V28" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W28" t="n">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="X28" t="n">
-        <v>3.44</v>
+        <v>3.4</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="Z28" t="n">
         <v>1.9</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.04</v>
+        <v>1.69</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.67</v>
+        <v>2.16</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['29', '39', '86', '90+1']</t>
         </is>
       </c>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>['14', '48', '70', '84']</t>
+          <t>['56', '78']</t>
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.08</v>
+        <v>1.53</v>
       </c>
       <c r="AI28" t="n">
-        <v>3.95</v>
+        <v>1.95</v>
       </c>
       <c r="AJ28" t="n">
-        <v>1.3</v>
+        <v>1.98</v>
       </c>
       <c r="AK28" s="3" t="n">
         <v>45764.54166666666</v>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,25 +4513,25 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="G32" t="n">
+        <v>3</v>
+      </c>
+      <c r="H32" t="n">
+        <v>1</v>
+      </c>
+      <c r="I32" t="n">
         <v>2</v>
       </c>
-      <c r="H32" t="n">
-        <v>2</v>
-      </c>
-      <c r="I32" t="n">
-        <v>1</v>
-      </c>
       <c r="J32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
@@ -4539,83 +4539,83 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.67</v>
+        <v>1.3</v>
       </c>
       <c r="M32" t="n">
-        <v>3.44</v>
+        <v>4.75</v>
       </c>
       <c r="N32" t="n">
-        <v>6.06</v>
+        <v>8.5</v>
       </c>
       <c r="O32" t="n">
-        <v>2.38</v>
+        <v>1.73</v>
       </c>
       <c r="P32" t="n">
-        <v>1.95</v>
+        <v>2.5</v>
       </c>
       <c r="Q32" t="n">
-        <v>6.44</v>
+        <v>7</v>
       </c>
       <c r="R32" t="n">
-        <v>1.47</v>
+        <v>1.29</v>
       </c>
       <c r="S32" t="n">
-        <v>2.4</v>
+        <v>3.25</v>
       </c>
       <c r="T32" t="n">
-        <v>3.2</v>
+        <v>2.37</v>
       </c>
       <c r="U32" t="n">
-        <v>1.32</v>
+        <v>1.51</v>
       </c>
       <c r="V32" t="n">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="W32" t="n">
-        <v>1.43</v>
+        <v>1.2</v>
       </c>
       <c r="X32" t="n">
-        <v>2.4</v>
+        <v>4.2</v>
       </c>
       <c r="Y32" t="n">
-        <v>2.6</v>
+        <v>1.65</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.53</v>
+        <v>2.15</v>
       </c>
       <c r="AA32" t="n">
-        <v>4.5</v>
+        <v>2.65</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.17</v>
+        <v>1.44</v>
       </c>
       <c r="AC32" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
-          <t>['27', '66']</t>
+          <t>['10', '45', '80']</t>
         </is>
       </c>
       <c r="AF32" t="inlineStr">
         <is>
-          <t>['41', '89']</t>
+          <t>['62']</t>
         </is>
       </c>
       <c r="AG32" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AI32" t="n">
         <v>1.3</v>
       </c>
-      <c r="AH32" t="n">
-        <v>2</v>
-      </c>
-      <c r="AI32" t="n">
-        <v>1.62</v>
-      </c>
       <c r="AJ32" t="n">
-        <v>2.89</v>
+        <v>4</v>
       </c>
       <c r="AK32" s="3" t="n">
         <v>45764.79166666666</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,109 +4642,109 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H33" t="n">
+        <v>2</v>
+      </c>
+      <c r="I33" t="n">
         <v>1</v>
       </c>
-      <c r="I33" t="n">
+      <c r="J33" t="n">
+        <v>1</v>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L33" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="M33" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="N33" t="n">
+        <v>6.06</v>
+      </c>
+      <c r="O33" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="P33" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>6.44</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="S33" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="T33" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="W33" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="X33" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>['27', '66']</t>
+        </is>
+      </c>
+      <c r="AF33" t="inlineStr">
+        <is>
+          <t>['41', '89']</t>
+        </is>
+      </c>
+      <c r="AG33" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH33" t="n">
         <v>2</v>
       </c>
-      <c r="J33" t="n">
-        <v>0</v>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L33" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="M33" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="N33" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="O33" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="P33" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>7</v>
-      </c>
-      <c r="R33" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S33" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T33" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="U33" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="V33" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W33" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X33" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AE33" t="inlineStr">
-        <is>
-          <t>['10', '45', '80']</t>
-        </is>
-      </c>
-      <c r="AF33" t="inlineStr">
-        <is>
-          <t>['62']</t>
-        </is>
-      </c>
-      <c r="AG33" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>3.3</v>
-      </c>
       <c r="AI33" t="n">
-        <v>1.3</v>
+        <v>1.62</v>
       </c>
       <c r="AJ33" t="n">
-        <v>4</v>
+        <v>2.89</v>
       </c>
       <c r="AK33" s="3" t="n">
         <v>45764.79166666666</v>
@@ -4900,25 +4900,25 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I35" t="n">
         <v>1</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -4926,83 +4926,83 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="M35" t="n">
-        <v>3</v>
+        <v>2.87</v>
       </c>
       <c r="N35" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="O35" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P35" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="Q35" t="n">
         <v>3.8</v>
       </c>
-      <c r="O35" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="P35" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>4.67</v>
-      </c>
       <c r="R35" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="S35" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="T35" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="W35" t="n">
         <v>1.5</v>
       </c>
-      <c r="S35" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="T35" t="n">
-        <v>3</v>
-      </c>
-      <c r="U35" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="V35" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W35" t="n">
-        <v>1.35</v>
-      </c>
       <c r="X35" t="n">
-        <v>2.9</v>
+        <v>2.47</v>
       </c>
       <c r="Y35" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="Z35" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AA35" t="n">
-        <v>4.05</v>
+        <v>4.8</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
-          <t>['26']</t>
+          <t>['10', '46']</t>
         </is>
       </c>
       <c r="AF35" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['45+3', '85']</t>
         </is>
       </c>
       <c r="AG35" t="n">
         <v>1.36</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="AI35" t="n">
-        <v>1.53</v>
+        <v>1.88</v>
       </c>
       <c r="AJ35" t="n">
-        <v>3</v>
+        <v>2.3</v>
       </c>
       <c r="AK35" s="3" t="n">
         <v>45764.83333333334</v>
@@ -5029,109 +5029,109 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
       </c>
       <c r="I36" t="n">
+        <v>1</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L36" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="M36" t="n">
         <v>3</v>
       </c>
-      <c r="J36" t="n">
-        <v>0</v>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L36" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="M36" t="n">
-        <v>3.79</v>
-      </c>
       <c r="N36" t="n">
-        <v>4.5</v>
+        <v>3.8</v>
       </c>
       <c r="O36" t="n">
-        <v>2.25</v>
+        <v>2.75</v>
       </c>
       <c r="P36" t="n">
-        <v>2.15</v>
+        <v>1.96</v>
       </c>
       <c r="Q36" t="n">
-        <v>5.03</v>
+        <v>4.67</v>
       </c>
       <c r="R36" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S36" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="T36" t="n">
+        <v>3</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="V36" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W36" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="X36" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE36" t="inlineStr">
+        <is>
+          <t>['26']</t>
+        </is>
+      </c>
+      <c r="AF36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG36" t="n">
         <v>1.36</v>
       </c>
-      <c r="S36" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T36" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="U36" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="V36" t="n">
-        <v>1</v>
-      </c>
-      <c r="W36" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X36" t="n">
-        <v>3.66</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AA36" t="n">
+      <c r="AH36" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AJ36" t="n">
         <v>3</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AE36" t="inlineStr">
-        <is>
-          <t>['5', '45+1', '45+3', '87']</t>
-        </is>
-      </c>
-      <c r="AF36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG36" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AH36" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AI36" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AJ36" t="n">
-        <v>2.85</v>
       </c>
       <c r="AK36" s="3" t="n">
         <v>45764.83333333334</v>
@@ -5158,109 +5158,109 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I37" t="n">
+        <v>3</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L37" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="M37" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="N37" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O37" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="P37" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>5.03</v>
+      </c>
+      <c r="R37" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S37" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V37" t="n">
         <v>1</v>
       </c>
-      <c r="J37" t="n">
-        <v>1</v>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L37" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="M37" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="N37" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="O37" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="P37" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="R37" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="S37" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="T37" t="n">
-        <v>3.56</v>
-      </c>
-      <c r="U37" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="V37" t="n">
-        <v>1.1</v>
-      </c>
       <c r="W37" t="n">
-        <v>1.5</v>
+        <v>1.22</v>
       </c>
       <c r="X37" t="n">
-        <v>2.47</v>
+        <v>3.66</v>
       </c>
       <c r="Y37" t="n">
-        <v>2.4</v>
+        <v>1.85</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.5</v>
+        <v>1.85</v>
       </c>
       <c r="AA37" t="n">
-        <v>4.8</v>
+        <v>3</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AC37" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AE37" t="inlineStr">
+        <is>
+          <t>['5', '45+1', '45+3', '87']</t>
+        </is>
+      </c>
+      <c r="AF37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG37" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AH37" t="n">
         <v>2.1</v>
       </c>
-      <c r="AD37" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AE37" t="inlineStr">
-        <is>
-          <t>['10', '46']</t>
-        </is>
-      </c>
-      <c r="AF37" t="inlineStr">
-        <is>
-          <t>['45+3', '85']</t>
-        </is>
-      </c>
-      <c r="AG37" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AH37" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AI37" t="n">
-        <v>1.88</v>
+        <v>1.62</v>
       </c>
       <c r="AJ37" t="n">
-        <v>2.3</v>
+        <v>2.85</v>
       </c>
       <c r="AK37" s="3" t="n">
         <v>45764.83333333334</v>
